--- a/artfynd/A 40206-2023 artfynd.xlsx
+++ b/artfynd/A 40206-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40206-2023 artfynd.xlsx
+++ b/artfynd/A 40206-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112069424</v>
+        <v>112370044</v>
       </c>
       <c r="B2" t="n">
-        <v>83087</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5589</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybodarna (Nybodarna), Jmt</t>
+          <t>nybodarna Österulvsås, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470097</v>
+        <v>470102</v>
       </c>
       <c r="R2" t="n">
-        <v>7039164</v>
+        <v>7039057</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112370038</v>
+        <v>112370045</v>
       </c>
       <c r="B3" t="n">
-        <v>77744</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469826</v>
+        <v>470217</v>
       </c>
       <c r="R3" t="n">
-        <v>7039235</v>
+        <v>7038987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112370045</v>
+        <v>112069424</v>
       </c>
       <c r="B4" t="n">
-        <v>90899</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1968</v>
+        <v>5589</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>nybodarna Österulvsås, Jmt</t>
+          <t>Nybodarna, Nybodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470217</v>
+        <v>470097</v>
       </c>
       <c r="R4" t="n">
-        <v>7038987</v>
+        <v>7039164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,12 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,33 +951,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112370040</v>
+        <v>112370041</v>
       </c>
       <c r="B5" t="n">
-        <v>77744</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +981,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>nybodarna Österulvsås, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470143</v>
+        <v>469969</v>
       </c>
       <c r="R5" t="n">
-        <v>7039263</v>
+        <v>7039249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,12 +1038,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1069,6 +1052,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,50 +1071,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112370044</v>
+        <v>112069043</v>
       </c>
       <c r="B6" t="n">
-        <v>85950</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>nybodarna Österulvsås, Jmt</t>
+          <t>Tjärnmyren, Tjärnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470103</v>
+        <v>469775</v>
       </c>
       <c r="R6" t="n">
-        <v>7039057</v>
+        <v>7039211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,12 +1139,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,72 +1153,64 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112370025</v>
+        <v>112370038</v>
       </c>
       <c r="B7" t="n">
-        <v>56527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>nybodarna Österulvsås, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469994</v>
+        <v>469826</v>
       </c>
       <c r="R7" t="n">
-        <v>7039247</v>
+        <v>7039235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,11 +1243,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,54 +1269,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112370007</v>
+        <v>112370039</v>
       </c>
       <c r="B8" t="n">
-        <v>56511</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>nybodarna Österulvsås, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469863</v>
+        <v>469889</v>
       </c>
       <c r="R8" t="n">
-        <v>7039172</v>
+        <v>7039252</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,11 +1340,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,54 +1366,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112370008</v>
+        <v>112370040</v>
       </c>
       <c r="B9" t="n">
-        <v>56511</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>nybodarna Österulvsås, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469854</v>
+        <v>470143</v>
       </c>
       <c r="R9" t="n">
-        <v>7039173</v>
+        <v>7039263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,17 +1431,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,15 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112370041</v>
+        <v>112370025</v>
       </c>
       <c r="B10" t="n">
-        <v>90935</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,26 +1474,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1565,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469969</v>
+        <v>469994</v>
       </c>
       <c r="R10" t="n">
-        <v>7039249</v>
+        <v>7039248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,13 +1540,17 @@
           <t>2023-09-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1628,15 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112370009</v>
+        <v>112370007</v>
       </c>
       <c r="B11" t="n">
-        <v>56511</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469795</v>
+        <v>469863</v>
       </c>
       <c r="R11" t="n">
-        <v>7039224</v>
+        <v>7039172</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,15 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112370039</v>
+        <v>112370008</v>
       </c>
       <c r="B12" t="n">
-        <v>77744</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,34 +1686,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>nybodarna Österulvsås, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469889</v>
+        <v>469854</v>
       </c>
       <c r="R12" t="n">
-        <v>7039252</v>
+        <v>7039173</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,6 +1750,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,15 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112370010</v>
+        <v>112370009</v>
       </c>
       <c r="B13" t="n">
-        <v>56511</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1885,10 +1820,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469821</v>
+        <v>469795</v>
       </c>
       <c r="R13" t="n">
-        <v>7039232</v>
+        <v>7039224</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,7 +1860,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112370037</v>
+        <v>112370010</v>
       </c>
       <c r="B14" t="n">
-        <v>89671</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,34 +1898,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>nybodarna Österulvsås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470039</v>
+        <v>469820</v>
       </c>
       <c r="R14" t="n">
-        <v>7039048</v>
+        <v>7039232</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2022,12 +1956,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,6 +1990,112 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112370014</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>nybodarna Österulvsås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>470208</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7039199</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40206-2023 artfynd.xlsx
+++ b/artfynd/A 40206-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370045</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112069424</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370041</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112069043</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370038</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370039</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370040</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1566,6 +1611,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370007</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1778,6 +1833,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370008</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370009</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370010</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,8 +2166,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112370014</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>